--- a/Packages/cn.etetet.brawl/Luban/Config/Datas/BrawlNPC.xlsx
+++ b/Packages/cn.etetet.brawl/Luban/Config/Datas/BrawlNPC.xlsx
@@ -10,7 +10,7 @@
   <sheets>
     <sheet name="BrawlNPC" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001" fullCalcOnLoad="1" fullPrecision="1"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
@@ -20,72 +20,90 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
-  <si>
-    <t>##var</t>
-  </si>
-  <si>
-    <t>Id</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>ModelPath</t>
-  </si>
-  <si>
-    <t>NPCType</t>
-  </si>
-  <si>
-    <t>BaseHp</t>
-  </si>
-  <si>
-    <t>HpGrowthPerLevel</t>
-  </si>
-  <si>
-    <t>MoveSpeedTier</t>
-  </si>
-  <si>
-    <t>ComponentTypes</t>
-  </si>
-  <si>
-    <t>ComponentValues</t>
-  </si>
-  <si>
-    <t>##type</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>(array#sep=,),int</t>
-  </si>
-  <si>
-    <t>##group</t>
-  </si>
-  <si>
-    <t>c</t>
-  </si>
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>NPC ID</t>
-  </si>
-  <si>
-    <t>名字</t>
-  </si>
-  <si>
-    <t>描述</t>
-  </si>
-  <si>
-    <t>模型路径</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="45">
+  <si>
+    <t xml:space="preserve">##var</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ModelPath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NPCType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BaseHp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HpGrowthPerLevel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MoveSpeedTier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ComponentTypes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ComponentValues</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CollisionLength</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CollisionHeight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CollisionWidth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PivotX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PivotZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">##type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">int</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(array#sep=,),int</t>
+  </si>
+  <si>
+    <t xml:space="preserve">float</t>
+  </si>
+  <si>
+    <t xml:space="preserve">##group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">##</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NPC ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">名字</t>
+  </si>
+  <si>
+    <t xml:space="preserve">描述</t>
+  </si>
+  <si>
+    <t xml:space="preserve">模型路径</t>
   </si>
   <si>
     <t xml:space="preserve">NPC类型
@@ -114,38 +132,70 @@
 4 非常快</t>
   </si>
   <si>
-    <t>组件类型数组</t>
-  </si>
-  <si>
-    <t>组件值数组</t>
-  </si>
-  <si>
-    <t>可摧毁墙</t>
-  </si>
-  <si>
-    <t>Wall_Tile_X</t>
-  </si>
-  <si>
-    <t>木桶</t>
-  </si>
-  <si>
-    <t>Wall_Tile_Barrel</t>
+    <t xml:space="preserve">组件类型数组</t>
+  </si>
+  <si>
+    <t xml:space="preserve">组件值数组</t>
+  </si>
+  <si>
+    <t xml:space="preserve">碰撞长度</t>
+  </si>
+  <si>
+    <t xml:space="preserve">碰撞高度</t>
+  </si>
+  <si>
+    <t xml:space="preserve">碰撞宽度
+等于0是圆柱
+大于0是长方体</t>
+  </si>
+  <si>
+    <t xml:space="preserve">中心点X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">中心点Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">可摧毁墙</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wall_Tile_X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">木桶</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wall_Tile_Barrel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">劫匪</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TerroristDefault</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="0" formatCode="General"/>
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <name val="Noto Sans SC"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
@@ -159,7 +209,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="11"/>
       <color rgb="FF222222"/>
       <name val="Microsoft YaHei"/>
@@ -167,7 +217,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="10"/>
       <color rgb="FF222222"/>
       <name val="Microsoft YaHei"/>
@@ -216,7 +266,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="1" diagonalDown="1">
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -224,48 +274,93 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="7">
-    <xf numFmtId="164" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" borderId="0" applyBorder="1" applyProtection="1" applyAlignment="1"/>
-    <xf numFmtId="43" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0"/>
-    <xf numFmtId="41" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0"/>
-    <xf numFmtId="44" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0"/>
-    <xf numFmtId="42" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0"/>
-    <xf numFmtId="9" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0"/>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" borderId="0" applyBorder="1" applyProtection="1" applyAlignment="1"/>
+  <cellStyleXfs count="21">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
-    <xf numFmtId="164" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1"/>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" borderId="0" applyBorder="0" xfId="0" applyProtection="1" applyAlignment="1"/>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" borderId="0" applyBorder="0" xfId="0" applyProtection="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="3" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1"/>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="3" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="4" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1"/>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="5" applyFont="1" fillId="3" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1"/>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="5" applyFont="1" fillId="3" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="5" applyFont="1" fillId="3" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="0" applyAlignment="0"/>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="5" applyFont="1" fillId="4" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1"/>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="5" applyFont="1" fillId="4" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="6" applyFont="1" fillId="4" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="4" applyFont="1" fillId="4" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1"/>
+  <cellXfs count="12">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
-    <cellStyle name="Currency" xfId="3" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
-    <cellStyle name="Percent" xfId="5" builtinId="5"/>
-    <cellStyle name="Normal" xfId="6"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="Normal" xfId="20"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -500,24 +595,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr xr2 ">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="2" width="16" customWidth="1" style="1"/>
-    <col min="3" max="3" width="11.54" customWidth="1" style="1"/>
-    <col min="4" max="5" width="26" customWidth="1" style="2"/>
-    <col min="6" max="6" width="16.27" customWidth="1" style="1"/>
-    <col min="7" max="8" width="18" customWidth="1" style="1"/>
-    <col min="9" max="9" width="26.57" customWidth="1" style="1"/>
-    <col min="10" max="11" width="18" customWidth="1" style="1"/>
-    <col min="16378" max="16384" width="11.53" customWidth="1" style="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="2" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="26.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="10" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="28.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="15" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16378" style="1" width="11.53"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -551,55 +648,85 @@
       <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="2" ht="26" customHeight="1">
+    <row r="2" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="J2" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>14</v>
+        <v>17</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="O2" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="P2" s="6" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="3" ht="26" customHeight="1">
+    <row r="3" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="6" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
@@ -607,98 +734,192 @@
       <c r="I3" s="6"/>
       <c r="J3" s="6"/>
       <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
     </row>
-    <row r="4" ht="121.6" customHeight="1">
-      <c r="A4" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" s="11" t="s">
+    <row r="4" customFormat="false" ht="121.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="B4" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="C4" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="J4" s="12" t="s">
+      <c r="D4" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="12" t="s">
+      <c r="E4" s="9" t="s">
         <v>27</v>
       </c>
+      <c r="F4" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="K4" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M4" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="N4" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="O4" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="P4" s="8" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="5" ht="25.35">
-      <c r="B5" s="1">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="1" t="n">
         <v>101</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" s="1">
-        <v>1</v>
-      </c>
-      <c r="G5" s="1">
+        <v>40</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="1" t="n">
         <v>5000</v>
       </c>
-      <c r="H5" s="1">
+      <c r="H5" s="1" t="n">
         <v>500</v>
       </c>
-      <c r="I5" s="1">
-        <v>0</v>
-      </c>
-      <c r="J5" s="1">
-        <v>1</v>
-      </c>
-      <c r="K5" s="1">
-        <v>1</v>
+      <c r="I5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="O5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
-    <row r="6" ht="25.35">
-      <c r="B6" s="1">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="1" t="n">
         <v>201</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6" s="1">
+        <v>42</v>
+      </c>
+      <c r="F6" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" s="1" t="n">
         <v>5000</v>
       </c>
-      <c r="H6" s="1">
+      <c r="H6" s="1" t="n">
         <v>500</v>
       </c>
-      <c r="I6" s="1">
-        <v>0</v>
-      </c>
-      <c r="J6" s="1">
-        <v>1</v>
-      </c>
-      <c r="K6" s="1">
-        <v>1</v>
+      <c r="I6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="1" t="n">
+        <v>301</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>500</v>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -710,9 +931,4 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=EPPlusLicense.txt>This workbook was created with the EPPlus library, licensed to ETET under the Polyform Noncommercial license, see https://polyformproject.org/licenses/noncommercial/1.0.0
-For more information about EPPlus, see https://epplussoftware.com/
-
 </file>
--- a/Packages/cn.etetet.brawl/Luban/Config/Datas/BrawlNPC.xlsx
+++ b/Packages/cn.etetet.brawl/Luban/Config/Datas/BrawlNPC.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="53">
   <si>
     <t xml:space="preserve">##var</t>
   </si>
@@ -40,6 +40,9 @@
     <t xml:space="preserve">NPCType</t>
   </si>
   <si>
+    <t xml:space="preserve">Faction</t>
+  </si>
+  <si>
     <t xml:space="preserve">BaseHp</t>
   </si>
   <si>
@@ -107,13 +110,20 @@
   </si>
   <si>
     <t xml:space="preserve">NPC类型
-1 暂定预留
-2 
+1 作战单位
+2 阻挡物
 3 
 4 
 5 
 6 
-7 </t>
+7 出生点</t>
+  </si>
+  <si>
+    <t xml:space="preserve">阵营
+0 中立敌对（和双方都敌对）
+1 红方（和蓝方敌对）
+2 蓝方（和红方敌对）
+3 中立友善（双方都友善）</t>
   </si>
   <si>
     <t xml:space="preserve">1 级基础生命值
@@ -171,6 +181,24 @@
   </si>
   <si>
     <t xml:space="preserve">TerroristDefault</t>
+  </si>
+  <si>
+    <t xml:space="preserve">能量水晶</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spawn_Gem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">出生点-红</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpawnZone_Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">出生点-蓝</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpawnZone_Blue</t>
   </si>
 </sst>
 </file>
@@ -303,7 +331,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -350,6 +378,10 @@
     </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -599,19 +631,20 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.54"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="2" width="26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="26.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="10" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="28.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="15" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16378" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="30.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="26.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="11" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="28.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="16" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16379" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -663,70 +696,76 @@
       <c r="P1" s="5" t="s">
         <v>15</v>
       </c>
+      <c r="Q1" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="G2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="H2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>17</v>
-      </c>
       <c r="I2" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L2" s="6" t="s">
         <v>20</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="Q2" s="6" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
@@ -739,55 +778,59 @@
       <c r="N3" s="6"/>
       <c r="O3" s="6"/>
       <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="121.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4" s="10" t="s">
         <v>29</v>
       </c>
+      <c r="G4" s="9" t="s">
+        <v>30</v>
+      </c>
       <c r="H4" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="I4" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="I4" s="10" t="s">
         <v>32</v>
       </c>
+      <c r="J4" s="9" t="s">
+        <v>33</v>
+      </c>
       <c r="K4" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="L4" s="8" t="s">
         <v>34</v>
       </c>
+      <c r="L4" s="11" t="s">
+        <v>35</v>
+      </c>
       <c r="M4" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="N4" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="O4" s="8" t="s">
+      <c r="N4" s="8" t="s">
         <v>37</v>
       </c>
+      <c r="O4" s="9" t="s">
+        <v>38</v>
+      </c>
       <c r="P4" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="Q4" s="8" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -795,42 +838,45 @@
         <v>101</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="I5" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="M5" s="1" t="n">
         <v>1</v>
       </c>
       <c r="N5" s="1" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="O5" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -839,42 +885,45 @@
         <v>201</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>2</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="I6" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="M6" s="1" t="n">
         <v>1</v>
       </c>
       <c r="N6" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -883,42 +932,162 @@
         <v>301</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>500</v>
+      </c>
+      <c r="J7" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="1" t="n">
+        <v>1001</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="1" t="n">
+        <v>2001</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="G9" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="G7" s="1" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H7" s="1" t="n">
-        <v>500</v>
-      </c>
-      <c r="I7" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="J7" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" s="1" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M7" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="1" t="n">
+      <c r="H9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="1" t="n">
+        <v>2002</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="1" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Packages/cn.etetet.brawl/Luban/Config/Datas/BrawlNPC.xlsx
+++ b/Packages/cn.etetet.brawl/Luban/Config/Datas/BrawlNPC.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="57">
   <si>
     <t xml:space="preserve">##var</t>
   </si>
@@ -71,6 +71,12 @@
   </si>
   <si>
     <t xml:space="preserve">PivotZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DeathDuration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RespawnDelay </t>
   </si>
   <si>
     <t xml:space="preserve">##type</t>
@@ -142,7 +148,32 @@
 4 非常快</t>
   </si>
   <si>
-    <t xml:space="preserve">组件类型数组</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">组件类型数组
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">1 阻挡
+2 复活点
+3
+4
+5
+6</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">组件值数组</t>
@@ -163,6 +194,13 @@
   </si>
   <si>
     <t xml:space="preserve">中心点Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">死亡持续时间</t>
+  </si>
+  <si>
+    <t xml:space="preserve">死亡后重生时间
+（0代表不会再重生）</t>
   </si>
   <si>
     <t xml:space="preserve">可摧毁墙</t>
@@ -208,7 +246,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="10"/>
       <name val="Noto Sans SC"/>
@@ -266,6 +304,12 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF222222"/>
+      <name val="Microsoft YaHei"/>
+      <family val="0"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -377,7 +421,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -631,7 +675,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Q10"/>
+  <dimension ref="A1:S10"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="16"/>
@@ -643,7 +687,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="26.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="11" style="1" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="28.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="16" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="16" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="21.56"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16379" style="1" width="11.53"/>
   </cols>
   <sheetData>
@@ -699,73 +744,85 @@
       <c r="Q1" s="5" t="s">
         <v>16</v>
       </c>
+      <c r="R1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="5" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Q2" s="6" t="s">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="R2" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="S2" s="6" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
@@ -779,58 +836,66 @@
       <c r="O3" s="6"/>
       <c r="P3" s="6"/>
       <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="121.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="N4" s="8" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O4" s="9" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="P4" s="8" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="Q4" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
+      </c>
+      <c r="R4" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="S4" s="9" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -838,10 +903,10 @@
         <v>101</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>2</v>
@@ -877,6 +942,12 @@
         <v>0</v>
       </c>
       <c r="Q5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S5" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -885,10 +956,10 @@
         <v>201</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>2</v>
@@ -924,6 +995,12 @@
         <v>0</v>
       </c>
       <c r="Q6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S6" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -932,10 +1009,10 @@
         <v>301</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>1</v>
@@ -966,6 +1043,12 @@
       </c>
       <c r="Q7" s="1" t="n">
         <v>0</v>
+      </c>
+      <c r="R7" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="S7" s="1" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -973,10 +1056,10 @@
         <v>1001</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>4</v>
@@ -1007,6 +1090,12 @@
       </c>
       <c r="Q8" s="1" t="n">
         <v>0</v>
+      </c>
+      <c r="R8" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S8" s="1" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1014,10 +1103,10 @@
         <v>2001</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>7</v>
@@ -1034,6 +1123,12 @@
       <c r="J9" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="K9" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L9" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="M9" s="1" t="n">
         <v>1</v>
       </c>
@@ -1047,6 +1142,12 @@
         <v>0</v>
       </c>
       <c r="Q9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1055,10 +1156,10 @@
         <v>2002</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>7</v>
@@ -1075,6 +1176,12 @@
       <c r="J10" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="K10" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="M10" s="1" t="n">
         <v>1</v>
       </c>
@@ -1088,6 +1195,12 @@
         <v>0</v>
       </c>
       <c r="Q10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="1" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Packages/cn.etetet.brawl/Luban/Config/Datas/BrawlNPC.xlsx
+++ b/Packages/cn.etetet.brawl/Luban/Config/Datas/BrawlNPC.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="62">
   <si>
     <t xml:space="preserve">##var</t>
   </si>
@@ -79,6 +79,12 @@
     <t xml:space="preserve">RespawnDelay </t>
   </si>
   <si>
+    <t xml:space="preserve">UnitLayerMask</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BlocksMovement</t>
+  </si>
+  <si>
     <t xml:space="preserve">##type</t>
   </si>
   <si>
@@ -92,6 +98,9 @@
   </si>
   <si>
     <t xml:space="preserve">float</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bool</t>
   </si>
   <si>
     <t xml:space="preserve">##group</t>
@@ -148,32 +157,9 @@
 4 非常快</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">组件类型数组
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF222222"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">1 阻挡
-2 复活点
-3
-4
-5
-6</t>
-    </r>
+    <t xml:space="preserve">组件类型数组
+1 原阻挡组件（迁移到UnitLayerMask/BlocksMovement，本次移除墙桶引用）
+2 复活点</t>
   </si>
   <si>
     <t xml:space="preserve">组件值数组</t>
@@ -203,10 +189,16 @@
 （0代表不会再重生）</t>
   </si>
   <si>
+    <t xml:space="preserve">逻辑标签位：Hero=1，Monster=2，Battle=4，Tile=8，Grass=16，Destroyable=32。组合按位或；40=可摧毁墙/木桶，6=劫匪，0=不参与当前战斗碰撞。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">活着时是否阻挡英雄移动；死亡后不阻挡。与弹丸碰撞规则独立。</t>
+  </si>
+  <si>
     <t xml:space="preserve">可摧毁墙</t>
   </si>
   <si>
-    <t xml:space="preserve">Wall_Tile_X</t>
+    <t xml:space="preserve">Wall_Tile_Wights</t>
   </si>
   <si>
     <t xml:space="preserve">木桶</t>
@@ -243,10 +235,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="&quot;TRUE&quot;;&quot;TRUE&quot;;&quot;FALSE&quot;"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <name val="Noto Sans SC"/>
@@ -304,12 +297,6 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF222222"/>
-      <name val="Microsoft YaHei"/>
-      <family val="0"/>
-    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -375,7 +362,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -400,6 +387,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -422,6 +413,14 @@
     </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -675,7 +674,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:S10"/>
+  <dimension ref="A1:U10"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="16"/>
@@ -689,6 +688,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="28.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="16" style="1" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="21.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="20" style="1" width="35"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16379" style="1" width="11.53"/>
   </cols>
   <sheetData>
@@ -750,152 +750,172 @@
       <c r="S1" s="5" t="s">
         <v>18</v>
       </c>
+      <c r="T1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="6" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" s="6" t="s">
+      <c r="A2" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="K2" s="6" t="s">
+      <c r="B2" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="C2" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="M2" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N2" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="O2" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="P2" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q2" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="R2" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="S2" s="6" t="s">
-        <v>23</v>
+      <c r="G2" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M2" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="N2" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="O2" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="P2" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q2" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="R2" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="S2" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="T2" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U2" s="6" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
+      <c r="A3" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7"/>
+      <c r="O3" s="7"/>
+      <c r="P3" s="7"/>
+      <c r="Q3" s="7"/>
+      <c r="R3" s="7"/>
+      <c r="S3" s="7"/>
+      <c r="T3" s="7"/>
+      <c r="U3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="121.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" s="9" t="s">
+      <c r="A4" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="B4" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="C4" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="D4" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="E4" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="F4" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="G4" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="K4" s="11" t="s">
+      <c r="H4" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="L4" s="11" t="s">
+      <c r="I4" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="M4" s="8" t="s">
+      <c r="J4" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="N4" s="8" t="s">
+      <c r="K4" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="O4" s="9" t="s">
+      <c r="L4" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="P4" s="8" t="s">
+      <c r="M4" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="Q4" s="8" t="s">
+      <c r="N4" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="R4" s="8" t="s">
+      <c r="O4" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="S4" s="9" t="s">
+      <c r="P4" s="9" t="s">
         <v>44</v>
+      </c>
+      <c r="Q4" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="R4" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="S4" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="T4" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="U4" s="13" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -903,10 +923,10 @@
         <v>101</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>2</v>
@@ -923,12 +943,6 @@
       <c r="J5" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="K5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="M5" s="1" t="n">
         <v>1</v>
       </c>
@@ -949,6 +963,12 @@
       </c>
       <c r="S5" s="1" t="n">
         <v>0</v>
+      </c>
+      <c r="T5" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="U5" s="14" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -956,10 +976,10 @@
         <v>201</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>2</v>
@@ -976,12 +996,6 @@
       <c r="J6" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="K6" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" s="1" t="n">
-        <v>2</v>
-      </c>
       <c r="M6" s="1" t="n">
         <v>1</v>
       </c>
@@ -1002,6 +1016,12 @@
       </c>
       <c r="S6" s="1" t="n">
         <v>0</v>
+      </c>
+      <c r="T6" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="U6" s="14" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1009,10 +1029,10 @@
         <v>301</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>1</v>
@@ -1049,6 +1069,12 @@
       </c>
       <c r="S7" s="1" t="n">
         <v>5</v>
+      </c>
+      <c r="T7" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="U7" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1056,10 +1082,10 @@
         <v>1001</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>4</v>
@@ -1096,6 +1122,12 @@
       </c>
       <c r="S8" s="1" t="n">
         <v>10</v>
+      </c>
+      <c r="T8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1103,10 +1135,10 @@
         <v>2001</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>54</v>
+        <v>58</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>59</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>7</v>
@@ -1148,6 +1180,12 @@
         <v>0</v>
       </c>
       <c r="S9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="14" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1156,10 +1194,10 @@
         <v>2002</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>56</v>
+        <v>60</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>61</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>7</v>
@@ -1201,6 +1239,12 @@
         <v>0</v>
       </c>
       <c r="S10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="14" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Packages/cn.etetet.brawl/Luban/Config/Datas/BrawlNPC.xlsx
+++ b/Packages/cn.etetet.brawl/Luban/Config/Datas/BrawlNPC.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="72">
   <si>
     <t xml:space="preserve">##var</t>
   </si>
@@ -198,7 +198,10 @@
     <t xml:space="preserve">可摧毁墙</t>
   </si>
   <si>
-    <t xml:space="preserve">Wall_Tile_Wights</t>
+    <t xml:space="preserve">Wall_Tile_Block1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRUE</t>
   </si>
   <si>
     <t xml:space="preserve">木桶</t>
@@ -213,6 +216,9 @@
     <t xml:space="preserve">TerroristDefault</t>
   </si>
   <si>
+    <t xml:space="preserve">FALSE</t>
+  </si>
+  <si>
     <t xml:space="preserve">能量水晶</t>
   </si>
   <si>
@@ -229,6 +235,30 @@
   </si>
   <si>
     <t xml:space="preserve">SpawnZone_Blue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">可摧毁墙2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wall_Tile_Block2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">木箱</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wall_Tile_Box</t>
+  </si>
+  <si>
+    <t xml:space="preserve">仙人掌</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wall_Tile_Cactus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">花盆</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wall_Tile_Vase</t>
   </si>
 </sst>
 </file>
@@ -237,7 +267,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="&quot;TRUE&quot;;&quot;TRUE&quot;;&quot;FALSE&quot;"/>
+    <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -362,7 +392,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -375,6 +405,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -387,7 +421,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -399,6 +433,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -415,12 +453,8 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -674,7 +708,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:U10"/>
+  <dimension ref="A1:U15"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="16"/>
@@ -688,233 +722,234 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="28.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="16" style="1" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="21.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="20" style="1" width="35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="3" width="35"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16379" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="N1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="O1" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="P1" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="Q1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="R1" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="S1" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="T1" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="6" t="s">
+      <c r="U1" s="7" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="K2" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="7" t="s">
+      <c r="L2" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="M2" s="7" t="s">
+      <c r="M2" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="N2" s="7" t="s">
+      <c r="N2" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="O2" s="7" t="s">
+      <c r="O2" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="P2" s="7" t="s">
+      <c r="P2" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="Q2" s="7" t="s">
+      <c r="Q2" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="R2" s="7" t="s">
+      <c r="R2" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="S2" s="7" t="s">
+      <c r="S2" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="T2" s="7" t="s">
+      <c r="T2" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="U2" s="6" t="s">
+      <c r="U2" s="10" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7" t="s">
+      <c r="B3" s="8"/>
+      <c r="C3" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
-      <c r="O3" s="7"/>
-      <c r="P3" s="7"/>
-      <c r="Q3" s="7"/>
-      <c r="R3" s="7"/>
-      <c r="S3" s="7"/>
-      <c r="T3" s="7"/>
-      <c r="U3" s="6"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
+      <c r="O3" s="8"/>
+      <c r="P3" s="8"/>
+      <c r="Q3" s="8"/>
+      <c r="R3" s="8"/>
+      <c r="S3" s="8"/>
+      <c r="T3" s="8"/>
+      <c r="U3" s="10"/>
     </row>
     <row r="4" customFormat="false" ht="121.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="J4" s="10" t="s">
+      <c r="J4" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="K4" s="12" t="s">
+      <c r="K4" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="L4" s="12" t="s">
+      <c r="L4" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="M4" s="9" t="s">
+      <c r="M4" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="N4" s="9" t="s">
+      <c r="N4" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="O4" s="10" t="s">
+      <c r="O4" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="P4" s="9" t="s">
+      <c r="P4" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="Q4" s="9" t="s">
+      <c r="Q4" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="R4" s="9" t="s">
+      <c r="R4" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="S4" s="10" t="s">
+      <c r="S4" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="T4" s="10" t="s">
+      <c r="T4" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="U4" s="13" t="s">
+      <c r="U4" s="15" t="s">
         <v>49</v>
       </c>
     </row>
@@ -967,8 +1002,8 @@
       <c r="T5" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="U5" s="14" t="b">
-        <v>1</v>
+      <c r="U5" s="3" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -976,10 +1011,10 @@
         <v>201</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>2</v>
@@ -1003,7 +1038,7 @@
         <v>1</v>
       </c>
       <c r="O6" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" s="1" t="n">
         <v>0</v>
@@ -1020,8 +1055,8 @@
       <c r="T6" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="U6" s="14" t="b">
-        <v>1</v>
+      <c r="U6" s="3" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1029,10 +1064,10 @@
         <v>301</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>1</v>
@@ -1073,8 +1108,8 @@
       <c r="T7" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="U7" s="14" t="b">
-        <v>0</v>
+      <c r="U7" s="3" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1082,10 +1117,10 @@
         <v>1001</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>4</v>
@@ -1126,8 +1161,8 @@
       <c r="T8" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="U8" s="14" t="b">
-        <v>0</v>
+      <c r="U8" s="3" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1135,10 +1170,10 @@
         <v>2001</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E9" s="15" t="s">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>61</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>7</v>
@@ -1185,8 +1220,8 @@
       <c r="T9" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="U9" s="14" t="b">
-        <v>0</v>
+      <c r="U9" s="3" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1194,10 +1229,10 @@
         <v>2002</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E10" s="15" t="s">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>63</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>7</v>
@@ -1244,8 +1279,273 @@
       <c r="T10" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="U10" s="14" t="b">
-        <v>0</v>
+      <c r="U10" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="1" t="n">
+        <v>102</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="U11" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="1" t="n">
+        <v>202</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="U12" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="1" t="n">
+        <v>203</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="U13" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="1" t="n">
+        <v>204</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="1" t="n">
+        <v>205</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="U15" s="3" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/Packages/cn.etetet.brawl/Luban/Config/Datas/BrawlNPC.xlsx
+++ b/Packages/cn.etetet.brawl/Luban/Config/Datas/BrawlNPC.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="74">
   <si>
     <t xml:space="preserve">##var</t>
   </si>
@@ -259,6 +259,12 @@
   </si>
   <si>
     <t xml:space="preserve">Wall_Tile_Vase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">宝箱（木桩）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chest</t>
   </si>
 </sst>
 </file>
@@ -708,7 +714,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:U15"/>
+  <dimension ref="A1:U16"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="16"/>
@@ -1548,6 +1554,59 @@
         <v>52</v>
       </c>
     </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="1" t="n">
+        <v>401</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I16" s="1" t="n">
+        <v>500</v>
+      </c>
+      <c r="J16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S16" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="U16" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
